--- a/daily_matches/job_matches_2026-09-10.xlsx
+++ b/daily_matches/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior GEN AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Flex Employee Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=520a6dbe77402b3e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>IT Undergraduate Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8138eb9cb9c4e58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Summer Intern 2027</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, XGBoost, LightGBM, S3, Athena, FastAPI, Docker</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932faec898cf8b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ABC Legal Services</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, XGBoost, LightGBM, CatBoost, AWS SageMaker, S3, Glue, Git</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39260bb57af31870</t>
+          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Generative AI Engineer - Hybrid</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42bff5c7d947468</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c760752270beadf</t>
+          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Internship, Machine Learning Engineer, Factory Software (Winter/Spring 2027)</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, OpenCV, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bf5b795be8fc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Backend Software Engineer I</t>
+          <t>AI Systems &amp; Solutions Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tandem Diabetes Care, Inc.</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milan, MO, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, MongoDB</t>
+          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fbb67af3c3dd38</t>
+          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Evinova</t>
+          <t>Sr. AI DevOps Developer- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631723e82c79799</t>
+          <t>https://www.indeed.com/viewjob?jk=8c453bb4f52952ec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Statistician</t>
+          <t>Korean Bilingual Sr. AI DevOps Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8f617ddc0f941c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Systems Engineer - IT Data Management</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Kafka, NoSQL, Python</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Databricks, PySpark, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Software Engineer 1 - IT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VSCO</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, MySQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
+          <t>https://www.indeed.com/viewjob?jk=997c2a168a7745a3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack JavaScript Developer (Data &amp; Search Focus)</t>
+          <t>Summer Associate Internship (Data Scientist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metric5</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, Git, Kafka, MySQL, SQL, R</t>
+          <t>Data Scientist, Copilot, AKS, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fad6da51118ce14</t>
+          <t>https://www.indeed.com/viewjob?jk=7a2b9d9ed0c60d79</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack JavaScript Developer (Data &amp; Search Focus)</t>
+          <t>Software Engineer III - Agentic AI, Java/Python</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metric5</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, Git, Kafka, MySQL, SQL, R</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d5af2eb9226b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=5247120208ea4bec</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Snowflake, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>Data Lake, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+          <t>Data Lake, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44812ef1c739fb2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fullstack AI &amp; Automation Engineer</t>
+          <t>Senior Data engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Automation Agency</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>RAG, S3, EC2, Glue, Athena, Redshift, Redshift, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c999cf7681e725d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Summer Intern 2027</t>
+          <t>Senior Core Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Docker, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515ab6055d77376</t>
+          <t>https://www.indeed.com/viewjob?jk=dce98c562a8e48ab</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Programmer / Artificial Intelligence Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APACHE STAINLESS EQUIPMENT CORP</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Beaver Dam, WI, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd292cb8fca77bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2f9562991aada7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a015b3f5ba31232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=28acafbe377bf788</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Antioch, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2743be5052447848</t>
+          <t>https://www.indeed.com/viewjob?jk=7984adba3af522af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Implementation Engineer</t>
+          <t>Full-Stack AI engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e33ec158ade71a</t>
+          <t>https://www.indeed.com/viewjob?jk=99ddbd2071d46956</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Implementation Engineer</t>
+          <t>Software Engineer -Gen AI Inferencing | BOFA | Onsite - (Dallas, Charlotte, New York)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Charlotte, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f7ec7034b0a78e6</t>
+          <t>https://www.indeed.com/viewjob?jk=357e6853ffaec632</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Implementation Engineer</t>
+          <t>Software Engineer - AI/RAG | BOFA | Onsite - (Dallas, Charlotte, New York)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Charlotte, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4a472d73b24c96</t>
+          <t>https://www.indeed.com/viewjob?jk=39a8ccea00e65e33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineering Intern (Part Time)</t>
+          <t>AI-GECX Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Terraform, Snowflake, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68963916e696102c</t>
+          <t>https://www.indeed.com/viewjob?jk=2764e318a12fdf61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern (Part Time)</t>
+          <t>The Cigna Group's Technology Development Program - AI Engineering Track Summer Internship</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Terraform, Snowflake, Redshift, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, Keras, Hadoop, Matplotlib, Python, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea71e6452d251b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5784e369bb7e85c3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer, WNBA</t>
+          <t>Full-Stack AI engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9013ca95404cf87e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ede9c26eee926f5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Senior Software Engineer- Infrastructure &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, Terraform, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7093e6367f58eb3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9def620f38bc18c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Summer 2027 Engineering Internships - Multiple Locations</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87bbe54c1675f11</t>
+          <t>https://www.indeed.com/viewjob?jk=baf5cb849e765f3f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Spring 2027 Engineering Internships - Multiple Locations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0090ad7809098ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=93fbe645fb6c10e4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad39868c1848da6</t>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665f342b6e3c479f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72fb7896b30ec741</t>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Science Analyst Revenue Management</t>
+          <t>Agentic AI Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, Tableau, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+          <t>AI Engineer, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c934a7859675095</t>
+          <t>https://www.indeed.com/viewjob?jk=74d835c15afafed6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>The Cigna Group's Technology Development Program - AI Engineering Track Summer Internship</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, Keras, Hadoop, Matplotlib, Python, R</t>
+          <t>Machine Learning Engineer, Kinesis, FastAPI, CI/CD, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a158f376301604ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3b71fadc3f885fa0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Machine Learning Scientist II - Agentic Experiences</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fb8f796b6a7701</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdd80d2c81a1ed0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8655de1e2f28eae3</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Tableau Developer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Metrc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8210810a291c7bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ed6f40724012bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
+          <t>Test Engineer, Features</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aircall</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athena, Synapse, Data Lake, Terraform, Git, Databricks, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, AKS, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+          <t>https://www.indeed.com/viewjob?jk=a1acdefc7e20d5a8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Workforce Management</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Fabric8Labs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,252 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d502044f4f71aff7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Software Development Engineering, Sr Advisor</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Coral Springs, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Kubernetes, Git, Snowflake, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a80f7e27488d6af</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CBIZ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Data Scientist, Copilot, S3, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44b48d8a2fc845b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Vendelux</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c56f8402b7218fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Agentic Ontology Software Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Databricks, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a674d4461826a16</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Scientist Intern</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MiTek</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5969d020cabd872</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>HDR</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Sioux Falls, SD, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e51240177f2f6e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Solutions Integration Engineer III</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=830c05c56b6b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=647187398781298e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-10.xlsx
+++ b/daily_matches/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,112 +486,112 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior GEN AI Engineer</t>
+          <t>AI-Powered Educational Assistant Developer (Part-Time)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flex Employee Services</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, ChromaDB, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520a6dbe77402b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1287681713bb14f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=07909a893cd39d21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Undergraduate Intern</t>
+          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8138eb9cb9c4e58</t>
+          <t>https://www.indeed.com/viewjob?jk=f8edd32bd73e07d6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f73ab0297cfa45f8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
+          <t>https://www.indeed.com/viewjob?jk=65919222b65c64ae</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8e455fefa50b5f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, MySQL, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1a17383b7cb48c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,207 +776,207 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a44235d5b6bd3a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Solutions Engineer</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
+          <t>https://www.indeed.com/viewjob?jk=ecca918c3e043bcb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. AI DevOps Developer- Bilingual (Korean/ English)</t>
+          <t>Data Engineer - Platform Innovation and Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c453bb4f52952ec</t>
+          <t>https://www.indeed.com/viewjob?jk=06686043f30ac2cf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Korean Bilingual Sr. AI DevOps Developer</t>
+          <t>Data Engineer - Platform Innovation and Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f617ddc0f941c</t>
+          <t>https://www.indeed.com/viewjob?jk=a082e0a91bf3760c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>AI-GECX Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Databricks, PySpark, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9da00fe7f334fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - IT</t>
+          <t>Engineer III (Full Stack)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997c2a168a7745a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8f32db1746800d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Scientist)</t>
+          <t>Test Automation Engineer, Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Acentra Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, AKS, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a2b9d9ed0c60d79</t>
+          <t>https://www.indeed.com/viewjob?jk=4846b7fa712409f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Agentic AI, Java/Python</t>
+          <t>Senior Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pharmavite LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>West Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,207 +1021,207 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5247120208ea4bec</t>
+          <t>https://www.indeed.com/viewjob?jk=0f056630ee522ef6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Generative AI Specialist Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b1e1b1d38d5873</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computational Scientist- HPC/AI Generalist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, PySpark, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python, R, Julia, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea111fd2c5e0a4d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>Senior Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M3, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lawrenceville, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Redshift, Redshift, PySpark, Python, SQL</t>
+          <t>Copilot, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fdc74cefffcaeec</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Core Infrastructure Engineer</t>
+          <t>Senior Data Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Campana &amp; Schott Business Services GmbH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Docker, Kafka, Python, R</t>
+          <t>Gemini, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce98c562a8e48ab</t>
+          <t>https://www.indeed.com/viewjob?jk=219f3194841bc7cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Technology Analyst – Data Science and Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2f9562991aada7</t>
+          <t>https://www.indeed.com/viewjob?jk=6bd751a53a0bb8da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Machine Learning Engineer - Payroll</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,137 +1231,137 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a015b3f5ba31232</t>
+          <t>https://www.indeed.com/viewjob?jk=bafae5c26f392ac4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/LLM Engineer — Healthcare Payment Integrity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
+          <t>RAG, LLaMA, FAISS, S3, Glue, Athena, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6af5867bc5eaed0e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
+          <t>RAG, MLflow, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
+          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Senior Applications Support Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>PDF Solutions, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28acafbe377bf788</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3f46ddac96af9b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Implementation Engineer</t>
+          <t>Finance Decision Optimization Team - Analytics Solutions Senior Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,269 +1371,269 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7984adba3af522af</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6e89c6ccbd9de7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-Stack AI engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ddbd2071d46956</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb7624aef8eff3d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer -Gen AI Inferencing | BOFA | Onsite - (Dallas, Charlotte, New York)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357e6853ffaec632</t>
+          <t>https://www.indeed.com/viewjob?jk=40381c8b6eb85af6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - AI/RAG | BOFA | Onsite - (Dallas, Charlotte, New York)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a8ccea00e65e33</t>
+          <t>https://www.indeed.com/viewjob?jk=de11be3f79d1a916</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI-GECX Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2764e318a12fdf61</t>
+          <t>https://www.indeed.com/viewjob?jk=b245285351c2a61c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Cigna Group's Technology Development Program - AI Engineering Track Summer Internship</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, Keras, Hadoop, Matplotlib, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5784e369bb7e85c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d41ad9b9fdf8fcc9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full-Stack AI engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ede9c26eee926f5</t>
+          <t>https://www.indeed.com/viewjob?jk=810e79f4c4d48ba2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Infrastructure &amp; Distributed Systems</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Terraform, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9def620f38bc18c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca4c75cc035e2b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Summer 2027 Engineering Internships - Multiple Locations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf5cb849e765f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f43b55229b8c9e9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Spring 2027 Engineering Internships - Multiple Locations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fbe645fb6c10e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c33b8a660dc2a55b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=15bfb6157e8d458c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=531022edfd9d8695</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Kafka, Cassandra, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad25181aed9f295</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer - Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d835c15afafed6</t>
+          <t>https://www.indeed.com/viewjob?jk=63e411b64994353f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Kinesis, FastAPI, CI/CD, Snowflake, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b71fadc3f885fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=fa168d7b68a7422f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist II - Agentic Experiences</t>
+          <t>Databricks AI &amp; Governance</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Git, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdd80d2c81a1ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f8f23805c8c3aae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Devops Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,112 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Metrc</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ed6f40724012bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Test Engineer, Features</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, AKS, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1acdefc7e20d5a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Fabric8Labs</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=647187398781298e</t>
+          <t>https://www.indeed.com/viewjob?jk=7edd6fbf1311eab5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-10.xlsx
+++ b/daily_matches/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
+          <t>https://www.indeed.com/viewjob?jk=4df4b455cb4162c0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Powered Educational Assistant Developer (Part-Time)</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, ChromaDB, Prompt Engineering, FastAPI, Docker</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1287681713bb14f</t>
+          <t>https://www.indeed.com/viewjob?jk=8075999ef8266fdb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Python AI Engineer / GenAI Backend Developer (1 – 2 Years)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BITCOT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,242 +566,242 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07909a893cd39d21</t>
+          <t>https://www.indeed.com/viewjob?jk=84097bdebd6e88f2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>AI Engineer, CI/CD, GitHub Actions, Git, MySQL, MongoDB, NoSQL, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8edd32bd73e07d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3607f6c3e5d11b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73ab0297cfa45f8</t>
+          <t>https://www.indeed.com/viewjob?jk=34a45510e8cd6a74</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65919222b65c64ae</t>
+          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8e455fefa50b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software engineer 1 – AI/ML Engineer (Generative AI)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1a17383b7cb48c</t>
+          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a44235d5b6bd3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecca918c3e043bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Platform Innovation and Engineering</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06686043f30ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa14d5b8cd87fc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Platform Innovation and Engineering</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,172 +881,172 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a082e0a91bf3760c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-GECX Engineer</t>
+          <t>Senior Software Engineer - Supply Chain (REMOTE)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9da00fe7f334fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec904f3971d4594</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer III (Full Stack)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8f32db1746800d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Test Automation Engineer, Senior</t>
+          <t>Sr Analyst, Marketing Data Product</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acentra Health</t>
+          <t>The Walt Disney Studios</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4846b7fa712409f6</t>
+          <t>https://www.indeed.com/viewjob?jk=56fc09bafabb9a94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Engineer</t>
+          <t>Data Scientist focus on Cybersecurity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pharmavite LLC</t>
+          <t>Information Unlimited, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>West Hills, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f056630ee522ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=340d21cbdf088b96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Generative AI Specialist Solutions Architect</t>
+          <t>Senior Azure DevOps &amp; Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b1e1b1d38d5873</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6737df4bf2df23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Computational Scientist- HPC/AI Generalist</t>
+          <t>Full Stack Engineer I/II (Java, APIs, AWS)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python, R, Julia, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea111fd2c5e0a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d253a2368f580f72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Agentic Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lawrenceville, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fdc74cefffcaeec</t>
+          <t>https://www.indeed.com/viewjob?jk=ff5bf1c88aa00762</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Consultant</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campana &amp; Schott Business Services GmbH</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219f3194841bc7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2386b967b590e1de</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technology Analyst – Data Science and Analytics</t>
+          <t>AI Engineer II / III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Kriya Therapeutics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bd751a53a0bb8da</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf9429688e0cbcb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Payroll</t>
+          <t>Agentic AI Engineer - Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>AI Engineer, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafae5c26f392ac4</t>
+          <t>https://www.indeed.com/viewjob?jk=65cd518272c4c54c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer — Healthcare Payment Integrity</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Codoxo</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,682 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, FAISS, S3, Glue, Athena, Kubernetes, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af5867bc5eaed0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Product Engineer (Databricks)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Applications Support Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PDF Solutions, Inc</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, Kafka, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3f46ddac96af9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Finance Decision Optimization Team - Analytics Solutions Senior Associate</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6e89c6ccbd9de7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb7624aef8eff3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40381c8b6eb85af6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CT, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de11be3f79d1a916</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b245285351c2a61c</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d41ad9b9fdf8fcc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=810e79f4c4d48ba2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca4c75cc035e2b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f43b55229b8c9e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c33b8a660dc2a55b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15bfb6157e8d458c</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=531022edfd9d8695</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad25181aed9f295</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63e411b64994353f</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa168d7b68a7422f</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Databricks AI &amp; Governance</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Git, Snowflake, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f8f23805c8c3aae</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Devops Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd6fbf1311eab5</t>
+          <t>https://www.indeed.com/viewjob?jk=20c53914e4da1492</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-10.xlsx
+++ b/daily_matches/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Jenkins, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4df4b455cb4162c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes</t>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Jenkins, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8075999ef8266fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python AI Engineer / GenAI Backend Developer (1 – 2 Years)</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BITCOT</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Git, PostgreSQL</t>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84097bdebd6e88f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, CI/CD, GitHub Actions, Git, MySQL, MongoDB, NoSQL, Power BI, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3607f6c3e5d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e1a5beee083cae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a45510e8cd6a74</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
+          <t>https://www.indeed.com/viewjob?jk=38c5e3dd352b7bd9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2289101d6b3d5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=24464d7f1d37c460</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>PeerSpace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Julia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
+          <t>https://www.indeed.com/viewjob?jk=188d399d5c02b54b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
+          <t>https://www.indeed.com/viewjob?jk=946462b46eca3a28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Zotec Partners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, Redshift, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa14d5b8cd87fc</t>
+          <t>https://www.indeed.com/viewjob?jk=686b0959bb1855b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer - Java Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lynchburg, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,392 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
+          <t>https://www.indeed.com/viewjob?jk=345dd67bd2b59c44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Supply Chain (REMOTE)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec904f3971d4594</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr Analyst, Marketing Data Product</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Walt Disney Studios</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Burbank, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56fc09bafabb9a94</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Scientist focus on Cybersecurity</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Information Unlimited, Inc.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=340d21cbdf088b96</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps &amp; Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Brown &amp; Brown Insurance</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6737df4bf2df23</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer I/II (Java, APIs, AWS)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d253a2368f580f72</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5bf1c88aa00762</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2386b967b590e1de</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Engineer II / III</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kriya Therapeutics</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf9429688e0cbcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer - Software Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65cd518272c4c54c</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Quality Assurance Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Western Alliance Bank</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20c53914e4da1492</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6986a673b69c5d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-10.xlsx
+++ b/daily_matches/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>Jr. AI Developer- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Jenkins, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=20fd6b227bbfafd2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Jenkins, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
+          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks, Power BI</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Glue, Synapse</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AI Engineer-Anthropic-Campus Hire - US East</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e1a5beee083cae</t>
+          <t>https://www.indeed.com/viewjob?jk=b3b8d81a5198c711</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AI Engineer-Anthropic-Campus Hire - US East</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=48939e5e5540dd70</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer-Anthropic-Campus Hire - US East</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38c5e3dd352b7bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3002ffcc85146a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer-Anthropic-Campus Hire - US East</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NewRocket</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2289101d6b3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0757d8b3ec4dae02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Java Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Weehawken, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24464d7f1d37c460</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b752139d7a57f5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PeerSpace</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Tableau, Python, SQL, R, Julia</t>
+          <t>RAG, Cortex, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188d399d5c02b54b</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, CI/CD, Git, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=946462b46eca3a28</t>
+          <t>https://www.indeed.com/viewjob?jk=f07ca17760ba8298</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Frontend Software Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zotec Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Redshift, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686b0959bb1855b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Java Development</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lynchburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,1267 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345dd67bd2b59c44</t>
+          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist, Merchandising Analytics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tractor Supply</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89cf28164d2b44e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior API Automation Engineer (AWS &amp; AI Testing)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Norfolk, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbcca40978bb697</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Auburn, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, CI/CD, GitHub Actions, Git, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6719ebfaf8aeca79</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>adonis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S3, EC2, FastAPI, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Feature Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Limited-Term)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Univeristy Of Colorado Boulder</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f22b837fc04cb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist - FP&amp;A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Subway</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae0c93e7d58df64e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Power BI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, S3, Data Lake, Git, Snowflake, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Analytics Engineer 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cityblock Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245aa1d1b857a6c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>REDICA Systems</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, FastAPI, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2436cd6f458174bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Git, Snowflake, PySpark, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Copart, Inc</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0144e1a64fdf9c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LexisNexis Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Horsham, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Horsham, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70a89b677df56a8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Black Book</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lawrenceville, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>11.1</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Kubernetes, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6986a673b69c5d</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99f4bd97c9f50c17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L3 Support Engineer - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, BigQuery, CI/CD, Terraform, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8dc1c454b7a495</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Microsoft AI Developer (Copilot Studio &amp; Azure AI)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Michael Baker International</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d98d46785a375e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>E T Consultant (Data Analyst)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d98cb22b03f6cbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Consumers Energy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b38369a4593373</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer II (IGEN)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>U.S. Venture, Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Appleton, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917108efc59aa768</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, Pinecone, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a76c2d82f6e3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Quantum Computing)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Infleqtion</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, AKS, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=328697e37276cc76</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Quantum Computing)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Infleqtion</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, AKS, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c88047d63416c058</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Quantum Computing)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Infleqtion</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, AKS, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d9aac029af63239</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, Terraform, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de7a39ff2650e308</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Applied Analytics and Production Solutions (Remote)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c4669abf36e0c09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Scientist – Drug Discovery &amp; R&amp;D Operations</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Elanco</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cb20371bb12ee96</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Shared Services</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e80e56b3ccc002d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef2bebe73a4f3cec</t>
         </is>
       </c>
     </row>
